--- a/data/trans_orig/CoPsoQ-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2012</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117619</t>
+          <t>118733</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151118</t>
+          <t>150791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54849</t>
+          <t>55291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82135</t>
+          <t>80452</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>182208</t>
+          <t>183188</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>223558</t>
+          <t>224128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43313</t>
+          <t>42304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70206</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32446</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56064</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83935</t>
+          <t>83374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>120733</t>
+          <t>118665</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60503</t>
+          <t>61585</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92547</t>
+          <t>92416</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32488</t>
+          <t>32841</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57938</t>
+          <t>54843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>101802</t>
+          <t>102184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>141245</t>
+          <t>139822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -1301,97 +1301,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>218448</t>
+          <t>218025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>259723</t>
+          <t>260551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>126760</t>
+          <t>125962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>159822</t>
+          <t>157881</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>356760</t>
+          <t>355474</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>412697</t>
+          <t>409047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56229</t>
+          <t>56664</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87482</t>
+          <t>88876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42482</t>
+          <t>43613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70238</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>106671</t>
+          <t>109683</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149123</t>
+          <t>149276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72071</t>
+          <t>73493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>106815</t>
+          <t>108432</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>51534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81291</t>
+          <t>81365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131092</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179384</t>
+          <t>178022</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -1870,97 +1870,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2116</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2128</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169631</t>
+          <t>169536</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207496</t>
+          <t>207479</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>116350</t>
+          <t>115232</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>144693</t>
+          <t>145296</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>294220</t>
+          <t>294667</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>343643</t>
+          <t>342993</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53124</t>
+          <t>51311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84485</t>
+          <t>83755</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50334</t>
+          <t>50752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>85858</t>
+          <t>84569</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123598</t>
+          <t>125526</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47722</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>79751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>30139</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54204</t>
+          <t>53975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83914</t>
+          <t>83926</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>125614</t>
+          <t>124097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -2439,97 +2439,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227333</t>
+          <t>226236</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268212</t>
+          <t>267213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>145489</t>
+          <t>143734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>179654</t>
+          <t>177933</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>383901</t>
+          <t>382259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437305</t>
+          <t>437300</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58841</t>
+          <t>58193</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>91659</t>
+          <t>90268</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53482</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82835</t>
+          <t>83555</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121406</t>
+          <t>119552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165109</t>
+          <t>167270</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>70634</t>
+          <t>71966</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107024</t>
+          <t>107430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>55983</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84972</t>
+          <t>85475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135026</t>
+          <t>133788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>181140</t>
+          <t>179773</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -3008,97 +3008,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>769749</t>
+          <t>774730</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846847</t>
+          <t>848278</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>472183</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>532756</t>
+          <t>534587</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1262592</t>
+          <t>1269457</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1362660</t>
+          <t>1370213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>240014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>298568</t>
+          <t>300717</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>182765</t>
+          <t>181284</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>231805</t>
+          <t>232626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>437644</t>
+          <t>432411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>517798</t>
+          <t>513223</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>284968</t>
+          <t>280709</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>350336</t>
+          <t>345507</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>193059</t>
+          <t>195098</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>246162</t>
+          <t>245692</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>491825</t>
+          <t>490640</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>572755</t>
+          <t>576318</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2016</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3809,97 +3809,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118233</t>
+          <t>119683</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150735</t>
+          <t>151126</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>49,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>67674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>91135</t>
+          <t>92872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195852</t>
+          <t>194791</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235772</t>
+          <t>235528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>57,35%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68189</t>
+          <t>67947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>26208</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47918</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74173</t>
+          <t>74919</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106990</t>
+          <t>109278</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,61%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40815</t>
+          <t>40945</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67176</t>
+          <t>66869</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>40772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>63745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87657</t>
+          <t>88747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123332</t>
+          <t>124923</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -4378,97 +4378,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2131</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2064</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>204084</t>
+          <t>201437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>245772</t>
+          <t>243156</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130646</t>
+          <t>131003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>164652</t>
+          <t>162841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345042</t>
+          <t>343661</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>400043</t>
+          <t>396849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>124969</t>
+          <t>127174</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47517</t>
+          <t>47954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74316</t>
+          <t>74459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143467</t>
+          <t>144353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190467</t>
+          <t>190791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>68853</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102144</t>
+          <t>100647</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>52497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79029</t>
+          <t>80652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129200</t>
+          <t>129495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172021</t>
+          <t>173919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -4947,97 +4947,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2129</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1952</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2054</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>203087</t>
+          <t>202293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>240603</t>
+          <t>241742</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>156368</t>
+          <t>158252</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>189898</t>
+          <t>189944</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>370512</t>
+          <t>372503</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>420495</t>
+          <t>423412</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58163</t>
+          <t>58499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91278</t>
+          <t>92654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42555</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69634</t>
+          <t>70077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>110890</t>
+          <t>108679</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154145</t>
+          <t>150958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,8%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>52881</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84855</t>
+          <t>85232</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30135</t>
+          <t>30540</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54291</t>
+          <t>53238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90329</t>
+          <t>90487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>128812</t>
+          <t>127981</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -5516,97 +5516,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1955</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178946</t>
+          <t>180596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219085</t>
+          <t>219345</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153387</t>
+          <t>151923</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188506</t>
+          <t>190471</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>342772</t>
+          <t>341987</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>396440</t>
+          <t>397946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>72997</t>
+          <t>71868</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104824</t>
+          <t>105382</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57687</t>
+          <t>58137</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>89570</t>
+          <t>87557</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138846</t>
+          <t>138880</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>181533</t>
+          <t>184028</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96489</t>
+          <t>96534</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133299</t>
+          <t>133588</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67802</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98161</t>
+          <t>97694</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>175330</t>
+          <t>171718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>222027</t>
+          <t>221469</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -6085,97 +6085,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>740569</t>
+          <t>745027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>818182</t>
+          <t>821252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>537174</t>
+          <t>540769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>602263</t>
+          <t>602641</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1302964</t>
+          <t>1300916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1407703</t>
+          <t>1401649</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>290444</t>
+          <t>289544</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353247</t>
+          <t>353561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>200413</t>
+          <t>199765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254435</t>
+          <t>254134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>501441</t>
+          <t>504803</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>590081</t>
+          <t>589018</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>289092</t>
+          <t>288229</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>356541</t>
+          <t>353114</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>216205</t>
+          <t>214666</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>270155</t>
+          <t>268141</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>519414</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>602280</t>
+          <t>603912</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,55%</t>
         </is>
       </c>
     </row>
@@ -6691,7 +6691,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2023</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6886,12 +6886,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>452657</t>
+          <t>450544</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>497202</t>
+          <t>494346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6901,12 +6901,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>490617</t>
+          <t>491686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>517186</t>
+          <t>517444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6936,12 +6936,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>950075</t>
+          <t>950485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1004676</t>
+          <t>1003158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -6999,12 +6999,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>27532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58880</t>
+          <t>58110</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23094</t>
+          <t>23375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45383</t>
+          <t>44515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56668</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94713</t>
+          <t>93385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -7112,12 +7112,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34494</t>
+          <t>32756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7147,12 +7147,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>10531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23431</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26982</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51711</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>17876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>47414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28661</t>
+          <t>28522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>33959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70701</t>
+          <t>68516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7455,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>377582</t>
+          <t>352845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>929132</t>
+          <t>928993</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7470,12 +7470,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672199</t>
+          <t>671272</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>707943</t>
+          <t>705516</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>925067</t>
+          <t>895366</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1624153</t>
+          <t>1623957</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -7568,12 +7568,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>29830</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>91540</t>
+          <t>90921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46470</t>
+          <t>46503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71514</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76251</t>
+          <t>82376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150213</t>
+          <t>149590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -7681,12 +7681,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22039</t>
+          <t>21197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>68098</t>
+          <t>67093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7696,12 +7696,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7716,12 +7716,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21095</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49844</t>
+          <t>49341</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99251</t>
+          <t>100063</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7794,12 +7794,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46151</t>
+          <t>45916</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>676681</t>
+          <t>704415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7809,12 +7809,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18047</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36084</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69829</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>867558</t>
+          <t>911802</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>501828</t>
+          <t>497257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>536920</t>
+          <t>535224</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8039,12 +8039,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>703767</t>
+          <t>704205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>779494</t>
+          <t>779949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1222251</t>
+          <t>1222524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1317862</t>
+          <t>1316677</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -8137,12 +8137,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45508</t>
+          <t>47812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8152,12 +8152,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8172,12 +8172,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61020</t>
+          <t>58224</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8187,12 +8187,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42528</t>
+          <t>44166</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93371</t>
+          <t>92944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29245</t>
+          <t>29217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8320,12 +8320,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21981</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50265</t>
+          <t>51588</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -8363,12 +8363,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17825</t>
+          <t>17635</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>41149</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8378,12 +8378,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8398,12 +8398,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37408</t>
+          <t>38852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70634</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>697920</t>
+          <t>700040</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>738028</t>
+          <t>739284</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>849709</t>
+          <t>850942</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>890597</t>
+          <t>890226</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1560791</t>
+          <t>1561559</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1621576</t>
+          <t>1622031</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42909</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8721,12 +8721,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21338</t>
+          <t>21845</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>44042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47043</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>77414</t>
+          <t>78020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8819,12 +8819,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25650</t>
+          <t>25766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52039</t>
+          <t>49982</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8854,12 +8854,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8889,12 +8889,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>42818</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71574</t>
+          <t>72449</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8932,12 +8932,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>28950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56180</t>
+          <t>54122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61963</t>
+          <t>61544</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97149</t>
+          <t>97211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1841028</t>
+          <t>1848070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2652915</t>
+          <t>2659127</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2759991</t>
+          <t>2761894</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2881710</t>
+          <t>2873844</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4503499</t>
+          <t>4490991</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5477779</t>
+          <t>5481471</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>126552</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198900</t>
+          <t>199545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9310,12 +9310,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126599</t>
+          <t>127200</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186795</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>272556</t>
+          <t>276505</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>367136</t>
+          <t>372829</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -9388,12 +9388,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>89689</t>
+          <t>85348</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149790</t>
+          <t>147090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9403,12 +9403,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>63787</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>102330</t>
+          <t>100828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9438,12 +9438,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>168305</t>
+          <t>172523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>239405</t>
+          <t>238420</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9473,12 +9473,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -9501,12 +9501,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>140378</t>
+          <t>138693</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1038337</t>
+          <t>1035544</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>80523</t>
+          <t>83290</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128698</t>
+          <t>128814</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>241897</t>
+          <t>236994</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1301515</t>
+          <t>1295377</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoPsoQ-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Habitat-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118733</t>
+          <t>115895</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150791</t>
+          <t>149853</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>55291</t>
+          <t>55302</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80452</t>
+          <t>79871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>183188</t>
+          <t>179972</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224128</t>
+          <t>221763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42304</t>
+          <t>42292</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68280</t>
+          <t>69681</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57837</t>
+          <t>58509</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83374</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118665</t>
+          <t>120769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>61585</t>
+          <t>62566</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92416</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32841</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54843</t>
+          <t>56501</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102184</t>
+          <t>102740</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139822</t>
+          <t>140316</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>218025</t>
+          <t>219547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>260551</t>
+          <t>259648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125962</t>
+          <t>127128</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157881</t>
+          <t>160377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>355474</t>
+          <t>354077</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>409047</t>
+          <t>409315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56664</t>
+          <t>56100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88876</t>
+          <t>88002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43613</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71291</t>
+          <t>71067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109683</t>
+          <t>107479</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>149276</t>
+          <t>150213</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>72371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108432</t>
+          <t>106785</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51534</t>
+          <t>50837</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>81365</t>
+          <t>80605</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>132566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>178022</t>
+          <t>176539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>169536</t>
+          <t>170799</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207479</t>
+          <t>208453</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>115232</t>
+          <t>115485</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>145296</t>
+          <t>143852</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>294667</t>
+          <t>295582</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>342993</t>
+          <t>341990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51311</t>
+          <t>51828</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83755</t>
+          <t>84176</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26755</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50752</t>
+          <t>48952</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84569</t>
+          <t>85427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>125006</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30139</t>
+          <t>30425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53975</t>
+          <t>55677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83926</t>
+          <t>84286</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124097</t>
+          <t>122922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226236</t>
+          <t>226242</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>267213</t>
+          <t>267913</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>143734</t>
+          <t>144131</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>177933</t>
+          <t>180030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>382259</t>
+          <t>385095</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>437300</t>
+          <t>437987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58193</t>
+          <t>58293</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>90268</t>
+          <t>92669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53745</t>
+          <t>53967</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83555</t>
+          <t>83286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>119552</t>
+          <t>120392</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167270</t>
+          <t>162353</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>71636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>107430</t>
+          <t>105514</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55983</t>
+          <t>53894</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>85475</t>
+          <t>84747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133788</t>
+          <t>134816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179773</t>
+          <t>178305</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,17%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>774730</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>848278</t>
+          <t>844525</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>469687</t>
+          <t>470536</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>534587</t>
+          <t>534354</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1269457</t>
+          <t>1265943</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1370213</t>
+          <t>1364162</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>240014</t>
+          <t>238459</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>300717</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181284</t>
+          <t>183497</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>232626</t>
+          <t>235905</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>432411</t>
+          <t>434119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>513223</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>280709</t>
+          <t>284308</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>345507</t>
+          <t>350478</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>245692</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>490640</t>
+          <t>490964</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>576318</t>
+          <t>571919</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119683</t>
+          <t>120467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151126</t>
+          <t>151351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67674</t>
+          <t>67838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92872</t>
+          <t>92168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194791</t>
+          <t>194055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>235528</t>
+          <t>235899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,44%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67947</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26208</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>47349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109278</t>
+          <t>110261</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40945</t>
+          <t>42020</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66869</t>
+          <t>67261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40772</t>
+          <t>40027</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63745</t>
+          <t>64067</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88747</t>
+          <t>87988</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124923</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>201437</t>
+          <t>202382</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243156</t>
+          <t>244793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131003</t>
+          <t>132571</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>162841</t>
+          <t>164508</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343661</t>
+          <t>343882</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>396849</t>
+          <t>397971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89176</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127174</t>
+          <t>124111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47954</t>
+          <t>48804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74459</t>
+          <t>76144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144353</t>
+          <t>145384</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190791</t>
+          <t>188754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>68853</t>
+          <t>68740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100647</t>
+          <t>102187</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52497</t>
+          <t>52401</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>79680</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129495</t>
+          <t>129940</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173919</t>
+          <t>173225</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,19%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>202293</t>
+          <t>201018</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>241742</t>
+          <t>240903</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>158252</t>
+          <t>159969</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>189944</t>
+          <t>189714</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>372503</t>
+          <t>372128</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>423412</t>
+          <t>420956</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>58499</t>
+          <t>59335</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92654</t>
+          <t>91936</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>42626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70077</t>
+          <t>69301</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108679</t>
+          <t>107381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150958</t>
+          <t>148419</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52881</t>
+          <t>52199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85232</t>
+          <t>83424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53238</t>
+          <t>52971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>90487</t>
+          <t>92245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>127981</t>
+          <t>130198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5629,12 +5629,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>180596</t>
+          <t>180506</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219345</t>
+          <t>219711</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5644,12 +5644,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151923</t>
+          <t>152486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>190471</t>
+          <t>188139</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341987</t>
+          <t>342103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397946</t>
+          <t>396747</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>71868</t>
+          <t>71337</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>105566</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5757,12 +5757,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5777,12 +5777,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>58137</t>
+          <t>56853</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>87557</t>
+          <t>88294</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5812,12 +5812,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>138880</t>
+          <t>138505</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>184028</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5855,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>96534</t>
+          <t>96227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133588</t>
+          <t>132463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5890,12 +5890,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>66829</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>97694</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>171718</t>
+          <t>173785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>221469</t>
+          <t>222975</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,69%</t>
         </is>
       </c>
     </row>
@@ -6198,12 +6198,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>741230</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>821252</t>
+          <t>819477</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6213,12 +6213,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>540769</t>
+          <t>540879</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>602641</t>
+          <t>604002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1300916</t>
+          <t>1304801</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1401649</t>
+          <t>1404483</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6311,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>289544</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353561</t>
+          <t>355907</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254134</t>
+          <t>251522</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>504803</t>
+          <t>508623</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>589018</t>
+          <t>593410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -6424,12 +6424,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>353114</t>
+          <t>353064</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6459,12 +6459,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>214666</t>
+          <t>213218</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>268141</t>
+          <t>270388</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>519414</t>
+          <t>519396</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>603912</t>
+          <t>602496</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -6881,32 +6881,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>476316</t>
+          <t>518752</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>450544</t>
+          <t>492485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>494346</t>
+          <t>538906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6916,32 +6916,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>504875</t>
+          <t>546078</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>491686</t>
+          <t>526844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>517444</t>
+          <t>558894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6951,32 +6951,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>981191</t>
+          <t>1064831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>950485</t>
+          <t>1037811</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1003158</t>
+          <t>1090850</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -6994,32 +6994,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40594</t>
+          <t>45744</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>30463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58110</t>
+          <t>65411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7029,32 +7029,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32426</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>23375</t>
+          <t>27209</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44515</t>
+          <t>52431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7064,32 +7064,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>73020</t>
+          <t>82651</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>63144</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>93385</t>
+          <t>105224</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -7107,32 +7107,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20125</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11423</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32756</t>
+          <t>37240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7142,32 +7142,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16149</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7177,32 +7177,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>42129</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26366</t>
+          <t>31332</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>56468</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -7220,32 +7220,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>29325</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>18799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47414</t>
+          <t>42754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19358</t>
+          <t>21174</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28522</t>
+          <t>31245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>47528</t>
+          <t>50499</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33959</t>
+          <t>37737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68516</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -7333,17 +7333,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>565205</t>
+          <t>616917</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>565205</t>
+          <t>616917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>565205</t>
+          <t>616917</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>572808</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>572808</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>572808</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7403,17 +7403,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1138013</t>
+          <t>1240110</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138013</t>
+          <t>1240110</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1138013</t>
+          <t>1240110</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7450,32 +7450,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>717290</t>
+          <t>787133</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>352845</t>
+          <t>759780</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>928993</t>
+          <t>813464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7485,32 +7485,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>690787</t>
+          <t>778131</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671272</t>
+          <t>756920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>705516</t>
+          <t>794446</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7520,32 +7520,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1408077</t>
+          <t>1565265</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>895366</t>
+          <t>1530114</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1623957</t>
+          <t>1598504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>85,95%</t>
         </is>
       </c>
     </row>
@@ -7563,32 +7563,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>71938</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>54863</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>90921</t>
+          <t>91392</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>5,74%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>61352</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46503</t>
+          <t>48801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71558</t>
+          <t>75622</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>121495</t>
+          <t>133291</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82376</t>
+          <t>113686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149590</t>
+          <t>158377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -7676,32 +7676,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46627</t>
+          <t>51237</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21197</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67093</t>
+          <t>72149</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7711,32 +7711,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30251</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>24260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>45504</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>76878</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49341</t>
+          <t>67330</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100063</t>
+          <t>106097</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7789,32 +7789,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>284751</t>
+          <t>45675</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45916</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704415</t>
+          <t>64040</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7824,32 +7824,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>29606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>21267</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>40157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7859,32 +7859,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>310632</t>
+          <t>75282</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>59114</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>911802</t>
+          <t>95755</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -7902,17 +7902,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1112563</t>
+          <t>955984</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1112563</t>
+          <t>955984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1112563</t>
+          <t>955984</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7937,17 +7937,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>804519</t>
+          <t>903747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>804519</t>
+          <t>903747</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>804519</t>
+          <t>903747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7972,17 +7972,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1917082</t>
+          <t>1859731</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1917082</t>
+          <t>1859731</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1917082</t>
+          <t>1859731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8019,32 +8019,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>519739</t>
+          <t>594076</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>497257</t>
+          <t>570245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>535224</t>
+          <t>612441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8054,32 +8054,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>741226</t>
+          <t>588581</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704205</t>
+          <t>571514</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>779949</t>
+          <t>604251</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1260964</t>
+          <t>1182657</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1222524</t>
+          <t>1153947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1316677</t>
+          <t>1208357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -8132,32 +8132,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32236</t>
+          <t>38675</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47812</t>
+          <t>55103</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8167,32 +8167,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18638</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>58224</t>
+          <t>56828</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8202,32 +8202,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>82708</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>44166</t>
+          <t>67632</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>103100</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -8245,32 +8245,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>20522</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8280,32 +8280,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18160</t>
+          <t>20662</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8141</t>
+          <t>14356</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28636</t>
+          <t>30105</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8315,32 +8315,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>41183</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>29730</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51588</t>
+          <t>56925</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -8358,32 +8358,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>33927</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17635</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>55119</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8393,32 +8393,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24057</t>
+          <t>26836</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38852</t>
+          <t>39538</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8428,32 +8428,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>51333</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>44672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69873</t>
+          <t>80700</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,9%</t>
         </is>
       </c>
     </row>
@@ -8471,17 +8471,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>596753</t>
+          <t>687200</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>596753</t>
+          <t>687200</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>596753</t>
+          <t>687200</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8506,17 +8506,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>822050</t>
+          <t>680112</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>822050</t>
+          <t>680112</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>822050</t>
+          <t>680112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8541,17 +8541,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1418803</t>
+          <t>1367312</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1418803</t>
+          <t>1367312</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1418803</t>
+          <t>1367312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>720278</t>
+          <t>772920</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>749847</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>739284</t>
+          <t>791836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>869457</t>
+          <t>869275</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>850942</t>
+          <t>852751</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>890226</t>
+          <t>884524</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1589736</t>
+          <t>1642196</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1561559</t>
+          <t>1615453</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1622031</t>
+          <t>1669120</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>89,98%</t>
         </is>
       </c>
     </row>
@@ -8701,32 +8701,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20103</t>
+          <t>21787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>47936</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8736,32 +8736,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>31032</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>26407</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>47410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8771,32 +8771,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>60499</t>
+          <t>68474</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46393</t>
+          <t>55351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78020</t>
+          <t>88129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -8814,32 +8814,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>36863</t>
+          <t>36660</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25766</t>
+          <t>25557</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>52754</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8849,32 +8849,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>19902</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>28919</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8884,32 +8884,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>56031</t>
+          <t>56563</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42818</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>73089</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -8927,32 +8927,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41319</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>35455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54122</t>
+          <t>64320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8962,32 +8962,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>37197</t>
+          <t>40365</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>31080</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49359</t>
+          <t>51432</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8997,32 +8997,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>78516</t>
+          <t>87799</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61544</t>
+          <t>72042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>97211</t>
+          <t>107720</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -9040,17 +9040,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>827928</t>
+          <t>889697</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>827928</t>
+          <t>889697</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>827928</t>
+          <t>889697</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9075,17 +9075,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>956854</t>
+          <t>965334</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>956854</t>
+          <t>965334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>956854</t>
+          <t>965334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9110,17 +9110,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1784782</t>
+          <t>1855031</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1784782</t>
+          <t>1855031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1784782</t>
+          <t>1855031</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2433622</t>
+          <t>2672882</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1848070</t>
+          <t>2625824</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2659127</t>
+          <t>2718744</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2806345</t>
+          <t>2782065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2761894</t>
+          <t>2748091</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2873844</t>
+          <t>2814892</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5239968</t>
+          <t>5454948</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4490991</t>
+          <t>5393247</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5481471</t>
+          <t>5509344</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -9270,32 +9270,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>166193</t>
+          <t>189040</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>159160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>199545</t>
+          <t>220265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9305,32 +9305,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>159664</t>
+          <t>178084</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127200</t>
+          <t>156019</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186388</t>
+          <t>202712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9340,32 +9340,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>325857</t>
+          <t>367125</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>276505</t>
+          <t>331380</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>372829</t>
+          <t>412395</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -9383,32 +9383,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>121117</t>
+          <t>131514</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85348</t>
+          <t>108909</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>147090</t>
+          <t>159600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9418,32 +9418,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>83729</t>
+          <t>94255</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63787</t>
+          <t>78682</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>100828</t>
+          <t>112553</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9453,32 +9453,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>204845</t>
+          <t>225769</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>172523</t>
+          <t>199287</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>238420</t>
+          <t>256636</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -9496,32 +9496,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>381516</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>138693</t>
+          <t>128852</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1035544</t>
+          <t>191559</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9531,32 +9531,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>106493</t>
+          <t>117982</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>83290</t>
+          <t>99873</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>128814</t>
+          <t>139077</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9566,32 +9566,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>488010</t>
+          <t>274343</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>236994</t>
+          <t>241745</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1295377</t>
+          <t>311088</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -9609,17 +9609,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3102448</t>
+          <t>3149798</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9644,17 +9644,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3156231</t>
+          <t>3172386</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9679,17 +9679,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6258680</t>
+          <t>6322184</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
